--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7DCDCE-A09A-4065-9C75-ACE5EE56E7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436C28E5-865E-4C5F-ADC8-74054B5D3F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
   <si>
     <t>StoryID</t>
   </si>
@@ -335,7 +346,7 @@
   </si>
   <si>
     <r>
-      <t>拜见王</t>
+      <t>听</t>
     </r>
     <r>
       <rPr>
@@ -345,7 +356,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>爷</t>
+      <t>闻蕲</t>
     </r>
     <r>
       <rPr>
@@ -355,17 +366,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>，有什么我能帮上忙的？</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>犬子前几天突然病了，卧床不起。精神萎靡，食欲不振。小王请了好几位大夫，给开了好多方子，都不见好转。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>听</t>
+      <t>州李先生医</t>
     </r>
     <r>
       <rPr>
@@ -375,7 +376,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>闻蕲</t>
+      <t>术</t>
     </r>
     <r>
       <rPr>
@@ -385,7 +386,69 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>州李先生医</t>
+      <t>高明，特</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请先生来给犬子医治。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>night</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>shi_zi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>王爷有请</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>005_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>璧</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚恭王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>草民拜见王</t>
     </r>
     <r>
       <rPr>
@@ -395,7 +458,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>术</t>
+      <t>爷</t>
     </r>
     <r>
       <rPr>
@@ -405,64 +468,100 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>高明，特</t>
+      <t>，有什么我能帮上忙的？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世子</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>咳咳咳，父王…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>犬子前几天突然病了，卧床不起。精神萎靡，食欲不振。小王</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>请先生来给犬子医治。</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>night</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>shi_zi</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>王爷有请</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>005_01</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>李</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>东</t>
+      <t>请</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>了好几位大夫，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>璧</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>楚恭王</t>
+      <t>给</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>开了好多方子，都不见好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。眼见着人一天比一天瘦，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在这么下去怕是要坏事了…</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>先生，小王就这么一个儿子，请您救救孩子吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>before</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -474,7 +573,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -488,7 +587,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -509,7 +608,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -589,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -629,9 +728,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -910,23 +1018,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -964,18 +1072,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
@@ -985,7 +1093,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="b">
@@ -998,14 +1106,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="12"/>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="12"/>
     </row>
   </sheetData>
@@ -1019,14 +1127,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1238,7 +1346,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>13</v>
@@ -1258,7 +1366,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
@@ -1267,7 +1375,7 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1278,7 +1386,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>13</v>
@@ -1287,7 +1395,7 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1298,7 +1406,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>13</v>
@@ -1307,38 +1415,60 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="H15" s="16" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="16" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="15"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436C28E5-865E-4C5F-ADC8-74054B5D3F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9919D1-AE98-417B-BD1E-4AB76DA18CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="18900" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="57">
   <si>
     <t>StoryID</t>
   </si>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>res://Assets/Background/</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -562,6 +558,22 @@
   </si>
   <si>
     <t>before</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1039,51 +1051,51 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="J1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E2" s="1">
         <v>2</v>
@@ -1093,14 +1105,14 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1132,7 +1144,7 @@
     <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
@@ -1155,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>11</v>
@@ -1176,10 +1188,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1190,16 +1202,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1210,16 +1224,18 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1230,16 +1246,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="F5" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1250,16 +1268,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1270,16 +1290,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1290,16 +1312,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1310,16 +1334,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1335,7 +1361,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1346,16 +1372,18 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1366,16 +1394,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1386,16 +1416,18 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1406,16 +1438,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1426,18 +1460,20 @@
         <v>7</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>55</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1448,16 +1484,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="8" t="s">
+        <v>56</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9919D1-AE98-417B-BD1E-4AB76DA18CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EA12AF-728F-4652-9887-7AD8EF09E9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="59">
   <si>
     <t>StoryID</t>
   </si>
@@ -574,6 +563,13 @@
   </si>
   <si>
     <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/StoryNpc/shi_zi_before</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -581,11 +577,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -599,7 +595,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -620,7 +616,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -643,6 +639,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -729,8 +733,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -749,9 +751,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1029,24 +1033,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.265625" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1059,32 +1064,35 @@
       <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="17" t="s">
         <v>21</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1108,25 +1116,28 @@
         <v>42</v>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12"/>
-      <c r="J3" s="13"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10"/>
+      <c r="K3" s="11"/>
+    </row>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -1139,14 +1150,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1190,7 +1201,7 @@
       <c r="G2" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="12" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1459,20 +1470,20 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>52</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>55</v>
       </c>
       <c r="G15" s="3"/>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="14" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1494,19 +1505,19 @@
         <v>56</v>
       </c>
       <c r="G16" s="3"/>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="15"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="17"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EA12AF-728F-4652-9887-7AD8EF09E9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5716F155-1BA2-4D7E-9DFB-12C382FE81D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -569,7 +569,7 @@
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/shi_zi_before</t>
+    <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5716F155-1BA2-4D7E-9DFB-12C382FE81D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C9E037-C34C-4A92-AB8C-FD1C47C2244B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -581,7 +592,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -595,7 +606,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -616,7 +627,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -755,7 +766,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1034,24 +1045,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.265625" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.25" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1092,7 +1103,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1129,14 +1140,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -1150,14 +1161,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C9E037-C34C-4A92-AB8C-FD1C47C2244B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56F31A-8A73-45A0-9CA5-EB933F8AF7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10178" yWindow="3645" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
   <si>
     <t>StoryID</t>
   </si>
@@ -561,10 +550,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/spring.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -581,6 +566,22 @@
   </si>
   <si>
     <t>res://Assets/Portrait/StoryNpc/shi_zi/shi_zi_before.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_01.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_02.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_04.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/003/003_03.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -592,7 +593,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -606,7 +607,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -627,7 +628,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -766,7 +767,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1045,24 +1046,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.25" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.265625" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1092,7 @@
         <v>21</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>22</v>
@@ -1103,7 +1104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1128,7 +1129,7 @@
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>1</v>
@@ -1140,14 +1141,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="18">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="18">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="18">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -1161,14 +1162,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.06640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1210,7 +1211,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>27</v>
@@ -1231,7 +1232,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
@@ -1253,9 +1254,11 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1275,7 +1278,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
@@ -1297,7 +1300,7 @@
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
@@ -1319,7 +1322,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
@@ -1341,7 +1344,7 @@
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
@@ -1363,7 +1366,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
@@ -1401,9 +1404,11 @@
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="H11" s="3" t="s">
         <v>39</v>
       </c>
@@ -1423,7 +1428,7 @@
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
@@ -1445,9 +1450,11 @@
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="3"/>
+        <v>53</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="H13" s="3" t="s">
         <v>50</v>
       </c>
@@ -1467,7 +1474,7 @@
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
@@ -1491,9 +1498,8 @@
         <v>52</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="3"/>
+        <v>54</v>
+      </c>
       <c r="H15" s="14" t="s">
         <v>49</v>
       </c>
@@ -1513,7 +1519,7 @@
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E56F31A-8A73-45A0-9CA5-EB933F8AF7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8619C6B7-E03A-4757-9931-C3D074F5CFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10178" yWindow="3645" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="63">
   <si>
     <t>StoryID</t>
   </si>
@@ -582,6 +593,10 @@
   </si>
   <si>
     <t>res://Assets/Background/003/003_03.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>脾虚湿盛</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -593,7 +608,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -607,7 +622,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -628,7 +643,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -767,7 +782,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1046,24 +1061,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.265625" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.25" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1123,7 +1138,9 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="13" t="s">
+        <v>62</v>
+      </c>
       <c r="H2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1141,14 +1158,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="10"/>
       <c r="K3" s="11"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -1162,14 +1179,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.06640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8619C6B7-E03A-4757-9931-C3D074F5CFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC02983-11B7-4137-8877-2967877B3087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>StoryID</t>
   </si>
@@ -598,6 +598,10 @@
   <si>
     <t>脾虚湿盛</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -731,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -780,6 +784,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1060,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
@@ -1069,16 +1076,17 @@
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.25" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1098,28 +1106,31 @@
         <v>18</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1138,35 +1149,84 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="1" t="b">
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="C3" s="10"/>
-      <c r="K3" s="11"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="G3" s="18"/>
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="C4" s="10"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5" s="10"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="7:7">
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="7:7">
+      <c r="G20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC02983-11B7-4137-8877-2967877B3087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846F3458-D0BA-4272-A2FF-33033C1974D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1070,20 +1070,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.25" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846F3458-D0BA-4272-A2FF-33033C1974D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8C8205-2DC0-4A27-9C06-DA30A57E5553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
   <si>
     <t>StoryID</t>
   </si>
@@ -601,6 +601,10 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +686,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -704,6 +708,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -735,7 +745,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -785,6 +795,12 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1067,25 +1083,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1098,38 +1115,41 @@
       <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
@@ -1142,90 +1162,91 @@
       <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L2" s="1" t="b">
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="C3" s="10"/>
-      <c r="G3" s="18"/>
-      <c r="L3" s="11"/>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="H3" s="18"/>
+      <c r="N3" s="11"/>
+    </row>
+    <row r="4" spans="1:15">
       <c r="C4" s="10"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="1:15">
       <c r="C5" s="10"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="18"/>
+      <c r="H5" s="18"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="8:8">
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="8:8">
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="8:8">
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E8C8205-2DC0-4A27-9C06-DA30A57E5553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F41DC9-E8AA-4074-A2A1-7B9999724EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>StoryID</t>
   </si>
@@ -98,12 +87,6 @@
   </si>
   <si>
     <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
   </si>
   <si>
     <t>NpcID</t>
@@ -606,6 +589,22 @@
   <si>
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -616,7 +615,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -630,7 +629,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -651,7 +650,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -805,7 +804,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1083,26 +1082,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1116,54 +1118,60 @@
         <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="K1" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="17" t="s">
+      <c r="N1" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="N1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="20" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -1173,67 +1181,69 @@
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="1" t="b">
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3" s="11"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">
@@ -1259,14 +1269,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1308,10 +1318,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1322,18 +1332,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1344,20 +1354,20 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1368,18 +1378,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1390,18 +1400,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1412,18 +1422,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1434,18 +1444,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1456,18 +1466,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1483,7 +1493,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1494,20 +1504,20 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1518,18 +1528,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1540,20 +1550,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1564,18 +1574,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1586,19 +1596,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="H15" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1609,18 +1619,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F41DC9-E8AA-4074-A2A1-7B9999724EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FCEA73-929C-48CB-94B8-78BEE87A8556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
   <si>
     <t>StoryID</t>
   </si>
@@ -584,10 +595,6 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -615,7 +622,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -629,7 +636,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -650,7 +657,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -804,7 +811,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1082,29 +1089,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="54.1328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1124,13 +1130,13 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H1" s="16" t="s">
         <v>61</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
@@ -1138,26 +1144,23 @@
       <c r="K1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="19" t="s">
         <v>62</v>
       </c>
       <c r="M1" s="19" t="s">
         <v>63</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" s="19" t="s">
         <v>54</v>
       </c>
+      <c r="O1" s="20" t="s">
+        <v>20</v>
+      </c>
       <c r="P1" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="20" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
         <v>42</v>
       </c>
@@ -1189,61 +1192,60 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16">
       <c r="C3" s="10"/>
       <c r="H3" s="18"/>
-      <c r="P3" s="11"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" spans="1:16">
       <c r="C4" s="10"/>
       <c r="H4" s="18"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16">
       <c r="C5" s="10"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16">
       <c r="H6" s="18"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16">
       <c r="H7" s="18"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16">
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16">
       <c r="H9" s="18"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16">
       <c r="H10" s="18"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16">
       <c r="H11" s="18"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16">
       <c r="H12" s="18"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16">
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16">
       <c r="H14" s="18"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16">
       <c r="H15" s="18"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16">
       <c r="H16" s="18"/>
     </row>
     <row r="17" spans="8:8">
@@ -1269,14 +1271,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FCEA73-929C-48CB-94B8-78BEE87A8556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5BC34E-EC72-4F48-827D-0F4ABCBA9BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
   <si>
     <t>StoryID</t>
   </si>
@@ -101,10 +90,6 @@
   </si>
   <si>
     <t>NpcID</t>
-  </si>
-  <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>PlayOnce</t>
@@ -612,6 +597,10 @@
   <si>
     <t>TriggerEntryId</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -622,7 +611,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -636,7 +625,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -657,7 +646,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -811,7 +800,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1090,24 +1079,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1124,57 +1113,57 @@
         <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="16" t="s">
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>64</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>20</v>
-      </c>
       <c r="P1" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -1184,16 +1173,18 @@
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -1271,14 +1262,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1320,10 +1311,10 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1334,18 +1325,18 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1356,20 +1347,20 @@
         <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1380,18 +1371,18 @@
         <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1402,18 +1393,18 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1424,18 +1415,18 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1446,18 +1437,18 @@
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1468,18 +1459,18 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1495,7 +1486,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1506,20 +1497,20 @@
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1530,18 +1521,18 @@
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1552,20 +1543,20 @@
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1576,18 +1567,18 @@
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1598,19 +1589,19 @@
         <v>7</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1621,18 +1612,18 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:8">

--- a/DataTables/DetailText/剧情/005_01王爷有请.xlsx
+++ b/DataTables/DetailText/剧情/005_01王爷有请.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5BC34E-EC72-4F48-827D-0F4ABCBA9BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E42455F-A6C0-403A-8127-F32E17BA9CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="3525" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -559,22 +570,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Background/003/003_01.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/003/003_02.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/003/003_04.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/003/003_03.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>脾虚湿盛</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -601,6 +596,190 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_01.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_02.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_03.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>res://Assets/Background/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_04.png</t>
+    </r>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -611,7 +790,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -625,7 +804,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -646,7 +825,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -800,7 +979,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1079,24 +1258,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="54.1328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="54.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1119,25 +1298,25 @@
         <v>17</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H1" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>64</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M1" s="19" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>53</v>
@@ -1173,13 +1352,13 @@
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="K2" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1262,14 +1441,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1311,7 +1490,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>24</v>
@@ -1357,7 +1536,7 @@
         <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>27</v>
@@ -1507,7 +1686,7 @@
         <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>36</v>
@@ -1553,7 +1732,7 @@
         <v>50</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>47</v>
